--- a/docs/StructureDefinition-heart-rate.xlsx
+++ b/docs/StructureDefinition-heart-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-heart-rate.xlsx
+++ b/docs/StructureDefinition-heart-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-heart-rate.xlsx
+++ b/docs/StructureDefinition-heart-rate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -484,25 +484,29 @@
     <t>A code representing the the type of device used for this observation.  Should only be used if not implicit in the code found in `Observation.code`.</t>
   </si>
   <si>
-    <t>Observation.extension:measurmentDevice.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:measurmentDevice.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>example</t>
@@ -571,10 +575,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Observation.extension:measurmentDevice.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -862,10 +862,6 @@
   </si>
   <si>
     <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Observation.category:VSCat.extension</t>
@@ -3633,7 +3629,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3659,10 +3655,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3685,13 +3681,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3742,7 +3738,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3751,7 +3747,7 @@
         <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
@@ -3766,7 +3762,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3777,10 +3773,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3851,7 +3847,7 @@
         <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
@@ -3860,7 +3856,7 @@
         <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3895,10 +3891,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3924,13 +3920,13 @@
         <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3938,7 +3934,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -3980,7 +3976,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -4015,10 +4011,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4041,13 +4037,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4074,27 +4070,27 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4103,7 +4099,7 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -4132,7 +4128,7 @@
         <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>180</v>
@@ -4157,13 +4153,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4212,7 +4208,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4221,7 +4217,7 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -4461,7 +4457,7 @@
         <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>144</v>
@@ -4490,7 +4486,7 @@
         <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4513,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4570,7 +4566,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4579,7 +4575,7 @@
         <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>20</v>
@@ -4594,7 +4590,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4608,7 +4604,7 @@
         <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4679,7 +4675,7 @@
         <v>141</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
@@ -4688,7 +4684,7 @@
         <v>142</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4726,7 +4722,7 @@
         <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4752,13 +4748,13 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4808,7 +4804,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>93</v>
@@ -4846,7 +4842,7 @@
         <v>196</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4869,13 +4865,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4914,17 +4910,17 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4933,7 +4929,7 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>105</v>
@@ -4962,7 +4958,7 @@
         <v>197</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>180</v>
@@ -4987,13 +4983,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5042,7 +5038,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5051,7 +5047,7 @@
         <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>105</v>
@@ -6065,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>258</v>
@@ -6187,7 +6183,7 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>258</v>
@@ -6309,13 +6305,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6366,7 +6362,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6390,7 +6386,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6401,10 +6397,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6430,10 +6426,10 @@
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>215</v>
@@ -6477,7 +6473,7 @@
         <v>141</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
@@ -6486,7 +6482,7 @@
         <v>142</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6510,7 +6506,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6521,10 +6517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6547,19 +6543,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6608,7 +6604,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6629,10 +6625,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6643,10 +6639,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6669,13 +6665,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6726,7 +6722,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6750,7 +6746,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6761,10 +6757,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6790,10 +6786,10 @@
         <v>138</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>215</v>
@@ -6837,7 +6833,7 @@
         <v>141</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
@@ -6846,7 +6842,7 @@
         <v>142</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6870,7 +6866,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6881,10 +6877,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6910,65 +6906,65 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6989,10 +6985,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -7003,10 +6999,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7029,16 +7025,16 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7088,7 +7084,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7109,10 +7105,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7123,10 +7119,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7152,63 +7148,63 @@
         <v>113</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7229,10 +7225,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7243,10 +7239,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7269,17 +7265,17 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7328,7 +7324,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7349,10 +7345,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7363,10 +7359,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7389,19 +7385,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7450,7 +7446,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7471,10 +7467,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7485,10 +7481,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7511,19 +7507,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7572,7 +7568,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7593,10 +7589,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7607,14 +7603,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7633,19 +7629,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7673,11 +7669,11 @@
         <v>181</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7694,7 +7690,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -7709,30 +7705,30 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>357</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7755,13 +7751,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7812,7 +7808,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7836,7 +7832,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7847,10 +7843,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7876,10 +7872,10 @@
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>215</v>
@@ -7923,7 +7919,7 @@
         <v>141</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>20</v>
@@ -7932,7 +7928,7 @@
         <v>142</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7956,7 +7952,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7967,10 +7963,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7993,19 +7989,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8042,7 +8038,7 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -8052,7 +8048,7 @@
         <v>142</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8073,10 +8069,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8087,13 +8083,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -8115,19 +8111,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8176,7 +8172,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8197,10 +8193,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8211,10 +8207,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8237,13 +8233,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8294,7 +8290,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8318,7 +8314,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8329,10 +8325,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8358,10 +8354,10 @@
         <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>215</v>
@@ -8405,7 +8401,7 @@
         <v>141</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>20</v>
@@ -8414,7 +8410,7 @@
         <v>142</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8438,7 +8434,7 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8449,10 +8445,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8478,23 +8474,23 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>20</v>
@@ -8536,7 +8532,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8557,10 +8553,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8571,10 +8567,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8597,16 +8593,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8656,7 +8652,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8677,10 +8673,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8691,10 +8687,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8720,21 +8716,21 @@
         <v>113</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>20</v>
@@ -8776,7 +8772,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8797,10 +8793,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8811,10 +8807,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8837,17 +8833,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8896,7 +8892,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8917,10 +8913,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8931,10 +8927,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8957,19 +8953,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -9018,7 +9014,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9039,10 +9035,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -9053,10 +9049,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9079,19 +9075,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9140,7 +9136,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9161,10 +9157,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9175,10 +9171,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9201,19 +9197,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9262,7 +9258,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9277,19 +9273,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -9297,10 +9293,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9323,16 +9319,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9382,7 +9378,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9403,13 +9399,13 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9417,14 +9413,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9443,19 +9439,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9504,7 +9500,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9519,19 +9515,19 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9539,14 +9535,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9565,19 +9561,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9626,7 +9622,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9635,25 +9631,25 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AJ60" t="s" s="2">
+      <c r="AK60" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AK60" t="s" s="2">
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>20</v>
@@ -9661,10 +9657,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9687,16 +9683,16 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9746,7 +9742,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9767,13 +9763,13 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>20</v>
@@ -9781,10 +9777,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9807,17 +9803,17 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9866,7 +9862,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9881,19 +9877,19 @@
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>20</v>
@@ -9901,10 +9897,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9927,19 +9923,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9976,17 +9972,17 @@
         <v>20</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9995,7 +9991,7 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -10004,30 +10000,30 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>447</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>20</v>
@@ -10049,19 +10045,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10110,7 +10106,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10119,7 +10115,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10128,27 +10124,27 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>447</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10171,13 +10167,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10228,7 +10224,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10252,7 +10248,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10263,10 +10259,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10292,10 +10288,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>215</v>
@@ -10339,7 +10335,7 @@
         <v>141</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>20</v>
@@ -10348,7 +10344,7 @@
         <v>142</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10372,7 +10368,7 @@
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10383,10 +10379,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10409,19 +10405,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10470,7 +10466,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10491,10 +10487,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10505,10 +10501,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10534,20 +10530,20 @@
         <v>113</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q68" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q68" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="R68" t="s" s="2">
         <v>20</v>
@@ -10571,28 +10567,28 @@
         <v>250</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="Z68" t="s" s="2">
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10613,10 +10609,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10627,10 +10623,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10653,17 +10649,17 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10712,7 +10708,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10733,10 +10729,10 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10747,10 +10743,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10776,72 +10772,72 @@
         <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="S70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF70" t="s" s="2">
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10853,10 +10849,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10867,10 +10863,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10896,65 +10892,65 @@
         <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10975,10 +10971,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10989,10 +10985,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11015,19 +11011,19 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11055,37 +11051,37 @@
         <v>181</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI72" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -11100,7 +11096,7 @@
         <v>136</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -11111,14 +11107,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11137,19 +11133,19 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11178,7 +11174,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -11196,7 +11192,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11214,27 +11210,27 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11257,19 +11253,19 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11318,7 +11314,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11339,10 +11335,10 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11353,10 +11349,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11379,16 +11375,16 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11418,7 +11414,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11436,7 +11432,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11454,27 +11450,27 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>536</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11497,19 +11493,19 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11538,7 +11534,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -11556,7 +11552,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11577,10 +11573,10 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11591,10 +11587,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11617,16 +11613,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11676,7 +11672,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11694,27 +11690,27 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>553</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11737,16 +11733,16 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11796,7 +11792,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11814,27 +11810,27 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>562</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11857,19 +11853,19 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11918,7 +11914,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11930,19 +11926,19 @@
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AK79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11953,10 +11949,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11979,13 +11975,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12036,7 +12032,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12060,7 +12056,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12071,10 +12067,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12100,10 +12096,10 @@
         <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>215</v>
@@ -12156,7 +12152,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12180,7 +12176,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12191,14 +12187,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12220,10 +12216,10 @@
         <v>138</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>215</v>
@@ -12278,7 +12274,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12313,10 +12309,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12339,13 +12335,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12396,7 +12392,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12405,7 +12401,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12417,10 +12413,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12431,10 +12427,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12457,13 +12453,13 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12514,7 +12510,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12523,7 +12519,7 @@
         <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>105</v>
@@ -12535,10 +12531,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12549,10 +12545,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12575,19 +12571,19 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12615,11 +12611,11 @@
         <v>117</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
       </c>
@@ -12636,7 +12632,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12654,13 +12650,13 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN85" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12671,10 +12667,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12697,19 +12693,19 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12734,14 +12730,14 @@
         <v>20</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
       </c>
@@ -12758,7 +12754,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12776,13 +12772,13 @@
         <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AM86" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN86" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12793,10 +12789,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12819,17 +12815,17 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12878,7 +12874,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12902,7 +12898,7 @@
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12913,10 +12909,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12939,13 +12935,13 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12996,7 +12992,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13017,10 +13013,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13031,10 +13027,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13057,16 +13053,16 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13116,7 +13112,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13137,10 +13133,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13151,10 +13147,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13177,16 +13173,16 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13236,7 +13232,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13257,10 +13253,10 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13271,10 +13267,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13297,19 +13293,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13358,7 +13354,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13370,19 +13366,19 @@
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AK91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM91" t="s" s="2">
+      <c r="AN91" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13393,10 +13389,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13419,13 +13415,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13476,7 +13472,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13500,7 +13496,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13511,10 +13507,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13540,10 +13536,10 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>215</v>
@@ -13596,7 +13592,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13620,7 +13616,7 @@
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13631,14 +13627,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13660,10 +13656,10 @@
         <v>138</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>215</v>
@@ -13718,7 +13714,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13753,10 +13749,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13779,19 +13775,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13819,11 +13815,11 @@
         <v>181</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
       </c>
@@ -13840,7 +13836,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>93</v>
@@ -13858,16 +13854,16 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>20</v>
@@ -13875,10 +13871,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13901,19 +13897,19 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>649</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13941,37 +13937,37 @@
         <v>181</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="Z96" t="s" s="2">
+      <c r="AA96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI96" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>105</v>
@@ -13980,27 +13976,27 @@
         <v>20</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>447</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14023,19 +14019,19 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N97" t="s" s="2">
-        <v>657</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14063,11 +14059,11 @@
         <v>181</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
       </c>
@@ -14084,7 +14080,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14093,7 +14089,7 @@
         <v>93</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>105</v>
@@ -14108,7 +14104,7 @@
         <v>136</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14119,14 +14115,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14145,19 +14141,19 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -14185,11 +14181,11 @@
         <v>181</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="Z98" t="s" s="2">
-        <v>661</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>20</v>
       </c>
@@ -14206,7 +14202,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14224,27 +14220,27 @@
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14270,16 +14266,16 @@
         <v>20</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>664</v>
-      </c>
       <c r="N99" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O99" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14328,7 +14324,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14349,10 +14345,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-heart-rate.xlsx
+++ b/docs/StructureDefinition-heart-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
